--- a/output/yearly_population_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_76_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4503</v>
+        <v>5877</v>
       </c>
       <c r="C2" t="n">
-        <v>12154</v>
+        <v>14908</v>
       </c>
       <c r="D2" t="n">
-        <v>24849</v>
+        <v>26209</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2813</v>
+        <v>3950</v>
       </c>
       <c r="C3" t="n">
-        <v>5478</v>
+        <v>4003</v>
       </c>
       <c r="D3" t="n">
-        <v>17089</v>
+        <v>14561</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2368</v>
+        <v>3202</v>
       </c>
       <c r="C4" t="n">
-        <v>5304</v>
+        <v>4326</v>
       </c>
       <c r="D4" t="n">
-        <v>7833</v>
+        <v>6523</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1558</v>
+        <v>1893</v>
       </c>
       <c r="C5" t="n">
-        <v>5000</v>
+        <v>4784</v>
       </c>
       <c r="D5" t="n">
-        <v>2869</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>877</v>
+        <v>938</v>
       </c>
       <c r="C6" t="n">
-        <v>4234</v>
+        <v>3522</v>
       </c>
       <c r="D6" t="n">
-        <v>1163</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="C7" t="n">
-        <v>2773</v>
+        <v>1973</v>
       </c>
       <c r="D7" t="n">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C8" t="n">
-        <v>1332</v>
+        <v>913</v>
       </c>
       <c r="D8" t="n">
-        <v>421</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>519</v>
+        <v>377</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5014</v>
+        <v>6393</v>
       </c>
       <c r="C2" t="n">
-        <v>11184</v>
+        <v>16493</v>
       </c>
       <c r="D2" t="n">
-        <v>32030</v>
+        <v>30023</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2866</v>
+        <v>3913</v>
       </c>
       <c r="C3" t="n">
-        <v>7357</v>
+        <v>7884</v>
       </c>
       <c r="D3" t="n">
-        <v>16961</v>
+        <v>15166</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2185</v>
+        <v>3016</v>
       </c>
       <c r="C4" t="n">
-        <v>5221</v>
+        <v>4080</v>
       </c>
       <c r="D4" t="n">
-        <v>9016</v>
+        <v>7636</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1673</v>
+        <v>2158</v>
       </c>
       <c r="C5" t="n">
-        <v>5030</v>
+        <v>4427</v>
       </c>
       <c r="D5" t="n">
-        <v>3469</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1059</v>
+        <v>1228</v>
       </c>
       <c r="C6" t="n">
-        <v>4477</v>
+        <v>4056</v>
       </c>
       <c r="D6" t="n">
-        <v>1381</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>533</v>
+        <v>572</v>
       </c>
       <c r="C7" t="n">
-        <v>3387</v>
+        <v>2635</v>
       </c>
       <c r="D7" t="n">
-        <v>721</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="C8" t="n">
-        <v>1897</v>
+        <v>1369</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>832</v>
+        <v>593</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>339</v>
+        <v>280</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7710</v>
+        <v>8588</v>
       </c>
       <c r="C2" t="n">
-        <v>14032</v>
+        <v>16171</v>
       </c>
       <c r="D2" t="n">
-        <v>26425</v>
+        <v>41573</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2991</v>
+        <v>4010</v>
       </c>
       <c r="C3" t="n">
-        <v>7873</v>
+        <v>10100</v>
       </c>
       <c r="D3" t="n">
-        <v>17846</v>
+        <v>15978</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2083</v>
+        <v>2911</v>
       </c>
       <c r="C4" t="n">
-        <v>5994</v>
+        <v>5599</v>
       </c>
       <c r="D4" t="n">
-        <v>9723</v>
+        <v>8414</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1668</v>
+        <v>2221</v>
       </c>
       <c r="C5" t="n">
-        <v>4952</v>
+        <v>4188</v>
       </c>
       <c r="D5" t="n">
-        <v>4075</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1175</v>
+        <v>1446</v>
       </c>
       <c r="C6" t="n">
-        <v>4607</v>
+        <v>4130</v>
       </c>
       <c r="D6" t="n">
-        <v>1643</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>652</v>
+        <v>739</v>
       </c>
       <c r="C7" t="n">
-        <v>3802</v>
+        <v>3179</v>
       </c>
       <c r="D7" t="n">
-        <v>790</v>
+        <v>777</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="C8" t="n">
-        <v>2417</v>
+        <v>1864</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C9" t="n">
-        <v>1199</v>
+        <v>875</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>504</v>
+        <v>390</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6887</v>
+        <v>7767</v>
       </c>
       <c r="C2" t="n">
-        <v>9878</v>
+        <v>11125</v>
       </c>
       <c r="D2" t="n">
-        <v>21996</v>
+        <v>34025</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3609</v>
+        <v>5008</v>
       </c>
       <c r="C3" t="n">
-        <v>11494</v>
+        <v>13818</v>
       </c>
       <c r="D3" t="n">
-        <v>19355</v>
+        <v>17156</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1541</v>
+        <v>2052</v>
       </c>
       <c r="C4" t="n">
-        <v>7918</v>
+        <v>7084</v>
       </c>
       <c r="D4" t="n">
-        <v>9109</v>
+        <v>7971</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1085</v>
+        <v>1336</v>
       </c>
       <c r="C5" t="n">
-        <v>4514</v>
+        <v>4047</v>
       </c>
       <c r="D5" t="n">
-        <v>2666</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>602</v>
+        <v>682</v>
       </c>
       <c r="C6" t="n">
-        <v>3725</v>
+        <v>3115</v>
       </c>
       <c r="D6" t="n">
-        <v>774</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="C7" t="n">
-        <v>2368</v>
+        <v>1826</v>
       </c>
       <c r="D7" t="n">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>1175</v>
+        <v>857</v>
       </c>
       <c r="D8" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>493</v>
+        <v>382</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4041</v>
+        <v>4553</v>
       </c>
       <c r="C2" t="n">
-        <v>4530</v>
+        <v>5183</v>
       </c>
       <c r="D2" t="n">
-        <v>16439</v>
+        <v>24851</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4184</v>
+        <v>5301</v>
       </c>
       <c r="C3" t="n">
-        <v>9830</v>
+        <v>11436</v>
       </c>
       <c r="D3" t="n">
-        <v>18609</v>
+        <v>18626</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1994</v>
+        <v>2779</v>
       </c>
       <c r="C4" t="n">
-        <v>9636</v>
+        <v>10311</v>
       </c>
       <c r="D4" t="n">
-        <v>10482</v>
+        <v>9127</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1194</v>
+        <v>1493</v>
       </c>
       <c r="C5" t="n">
-        <v>5900</v>
+        <v>5381</v>
       </c>
       <c r="D5" t="n">
-        <v>3378</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>699</v>
+        <v>823</v>
       </c>
       <c r="C6" t="n">
-        <v>4211</v>
+        <v>3588</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>935</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>2885</v>
+        <v>2327</v>
       </c>
       <c r="D7" t="n">
-        <v>508</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>1536</v>
+        <v>1130</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>513</v>
+        <v>429</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4197</v>
+        <v>4245</v>
       </c>
       <c r="C2" t="n">
-        <v>9870</v>
+        <v>13280</v>
       </c>
       <c r="D2" t="n">
-        <v>16664</v>
+        <v>22625</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3499</v>
+        <v>4239</v>
       </c>
       <c r="C3" t="n">
-        <v>6588</v>
+        <v>7603</v>
       </c>
       <c r="D3" t="n">
-        <v>17242</v>
+        <v>18220</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2460</v>
+        <v>3274</v>
       </c>
       <c r="C4" t="n">
-        <v>9526</v>
+        <v>10636</v>
       </c>
       <c r="D4" t="n">
-        <v>11311</v>
+        <v>10399</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1356</v>
+        <v>1796</v>
       </c>
       <c r="C5" t="n">
-        <v>7519</v>
+        <v>7540</v>
       </c>
       <c r="D5" t="n">
-        <v>4366</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>820</v>
+        <v>999</v>
       </c>
       <c r="C6" t="n">
-        <v>4885</v>
+        <v>4380</v>
       </c>
       <c r="D6" t="n">
-        <v>1287</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="C7" t="n">
-        <v>3457</v>
+        <v>2880</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="C8" t="n">
-        <v>2066</v>
+        <v>1609</v>
       </c>
       <c r="D8" t="n">
-        <v>344</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>878</v>
+        <v>687</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>300</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2520</v>
+        <v>2556</v>
       </c>
       <c r="C2" t="n">
-        <v>4845</v>
+        <v>6422</v>
       </c>
       <c r="D2" t="n">
-        <v>11761</v>
+        <v>15792</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3559</v>
+        <v>4129</v>
       </c>
       <c r="C3" t="n">
-        <v>7380</v>
+        <v>9139</v>
       </c>
       <c r="D3" t="n">
-        <v>16827</v>
+        <v>18269</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2699</v>
+        <v>3571</v>
       </c>
       <c r="C4" t="n">
-        <v>9431</v>
+        <v>10577</v>
       </c>
       <c r="D4" t="n">
-        <v>12049</v>
+        <v>11295</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1416</v>
+        <v>1837</v>
       </c>
       <c r="C5" t="n">
-        <v>9122</v>
+        <v>9291</v>
       </c>
       <c r="D5" t="n">
-        <v>4476</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>661</v>
+        <v>792</v>
       </c>
       <c r="C6" t="n">
-        <v>5806</v>
+        <v>5241</v>
       </c>
       <c r="D6" t="n">
-        <v>1249</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C7" t="n">
-        <v>3639</v>
+        <v>2966</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1447</v>
+        <v>1146</v>
       </c>
       <c r="D8" t="n">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3233</v>
+        <v>3269</v>
       </c>
       <c r="C2" t="n">
-        <v>6040</v>
+        <v>5898</v>
       </c>
       <c r="D2" t="n">
-        <v>15376</v>
+        <v>12099</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2696</v>
+        <v>2999</v>
       </c>
       <c r="C3" t="n">
-        <v>5615</v>
+        <v>7115</v>
       </c>
       <c r="D3" t="n">
-        <v>15074</v>
+        <v>16753</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2639</v>
+        <v>3344</v>
       </c>
       <c r="C4" t="n">
-        <v>8399</v>
+        <v>9708</v>
       </c>
       <c r="D4" t="n">
-        <v>12416</v>
+        <v>12022</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1697</v>
+        <v>2222</v>
       </c>
       <c r="C5" t="n">
-        <v>9062</v>
+        <v>9742</v>
       </c>
       <c r="D5" t="n">
-        <v>5473</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>850</v>
+        <v>1050</v>
       </c>
       <c r="C6" t="n">
-        <v>7205</v>
+        <v>6879</v>
       </c>
       <c r="D6" t="n">
-        <v>1635</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>239</v>
+        <v>287</v>
       </c>
       <c r="C7" t="n">
-        <v>4480</v>
+        <v>3892</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>2226</v>
+        <v>1792</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>674</v>
+        <v>561</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2046</v>
+        <v>2334</v>
       </c>
       <c r="C2" t="n">
-        <v>4142</v>
+        <v>3243</v>
       </c>
       <c r="D2" t="n">
-        <v>11121</v>
+        <v>8978</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2507</v>
+        <v>2702</v>
       </c>
       <c r="C3" t="n">
-        <v>5263</v>
+        <v>6127</v>
       </c>
       <c r="D3" t="n">
-        <v>14311</v>
+        <v>15347</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2441</v>
+        <v>2966</v>
       </c>
       <c r="C4" t="n">
-        <v>7397</v>
+        <v>8789</v>
       </c>
       <c r="D4" t="n">
-        <v>12489</v>
+        <v>12362</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1845</v>
+        <v>2425</v>
       </c>
       <c r="C5" t="n">
-        <v>8998</v>
+        <v>9808</v>
       </c>
       <c r="D5" t="n">
-        <v>6144</v>
+        <v>5746</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>979</v>
+        <v>1222</v>
       </c>
       <c r="C6" t="n">
-        <v>8030</v>
+        <v>7996</v>
       </c>
       <c r="D6" t="n">
-        <v>1942</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>214</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>5329</v>
+        <v>4830</v>
       </c>
       <c r="D7" t="n">
-        <v>717</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2798</v>
+        <v>2270</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>710</v>
+        <v>620</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
         <v>91</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3574</v>
+        <v>4193</v>
       </c>
       <c r="C2" t="n">
-        <v>8160</v>
+        <v>4494</v>
       </c>
       <c r="D2" t="n">
-        <v>17192</v>
+        <v>15675</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1982</v>
+        <v>2172</v>
       </c>
       <c r="C3" t="n">
-        <v>4372</v>
+        <v>4501</v>
       </c>
       <c r="D3" t="n">
-        <v>13060</v>
+        <v>13676</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2161</v>
+        <v>2501</v>
       </c>
       <c r="C4" t="n">
-        <v>6332</v>
+        <v>7532</v>
       </c>
       <c r="D4" t="n">
-        <v>12354</v>
+        <v>12387</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1855</v>
+        <v>2399</v>
       </c>
       <c r="C5" t="n">
-        <v>8196</v>
+        <v>9212</v>
       </c>
       <c r="D5" t="n">
-        <v>6690</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1163</v>
+        <v>1485</v>
       </c>
       <c r="C6" t="n">
-        <v>8318</v>
+        <v>8593</v>
       </c>
       <c r="D6" t="n">
-        <v>2441</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>387</v>
+        <v>474</v>
       </c>
       <c r="C7" t="n">
-        <v>6332</v>
+        <v>5945</v>
       </c>
       <c r="D7" t="n">
-        <v>853</v>
+        <v>841</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>3615</v>
+        <v>3144</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1351</v>
+        <v>1127</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>35</v>
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4717</v>
+        <v>4727</v>
       </c>
       <c r="C2" t="n">
-        <v>15535</v>
+        <v>7028</v>
       </c>
       <c r="D2" t="n">
-        <v>13329</v>
+        <v>7980</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2607</v>
+        <v>3063</v>
       </c>
       <c r="C2" t="n">
-        <v>4830</v>
+        <v>2660</v>
       </c>
       <c r="D2" t="n">
-        <v>12790</v>
+        <v>11662</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2682</v>
+        <v>3004</v>
       </c>
       <c r="C3" t="n">
-        <v>5619</v>
+        <v>4982</v>
       </c>
       <c r="D3" t="n">
-        <v>14449</v>
+        <v>14958</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2801</v>
+        <v>3473</v>
       </c>
       <c r="C4" t="n">
-        <v>9107</v>
+        <v>10599</v>
       </c>
       <c r="D4" t="n">
-        <v>12516</v>
+        <v>12462</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1091</v>
+        <v>1394</v>
       </c>
       <c r="C5" t="n">
-        <v>11880</v>
+        <v>12653</v>
       </c>
       <c r="D5" t="n">
-        <v>6036</v>
+        <v>5736</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>357</v>
+        <v>437</v>
       </c>
       <c r="C6" t="n">
-        <v>7591</v>
+        <v>7341</v>
       </c>
       <c r="D6" t="n">
-        <v>1907</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>3542</v>
+        <v>3081</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1323</v>
+        <v>1104</v>
       </c>
       <c r="D8" t="n">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
         <v>34</v>
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6777</v>
+        <v>5926</v>
       </c>
       <c r="C2" t="n">
-        <v>8354</v>
+        <v>6399</v>
       </c>
       <c r="D2" t="n">
-        <v>19222</v>
+        <v>18428</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="C3" t="n">
-        <v>7829</v>
+        <v>3542</v>
       </c>
       <c r="D3" t="n">
-        <v>2878</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4480</v>
+        <v>4377</v>
       </c>
       <c r="C2" t="n">
-        <v>6724</v>
+        <v>8110</v>
       </c>
       <c r="D2" t="n">
-        <v>20444</v>
+        <v>17975</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3602</v>
+        <v>3256</v>
       </c>
       <c r="C3" t="n">
-        <v>7007</v>
+        <v>4448</v>
       </c>
       <c r="D3" t="n">
-        <v>5411</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C4" t="n">
-        <v>4630</v>
+        <v>2117</v>
       </c>
       <c r="D4" t="n">
-        <v>1761</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4980,7 +4980,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="n">
         <v>172</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4764</v>
+        <v>4689</v>
       </c>
       <c r="C2" t="n">
-        <v>11456</v>
+        <v>7740</v>
       </c>
       <c r="D2" t="n">
-        <v>18427</v>
+        <v>17121</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3316</v>
+        <v>3130</v>
       </c>
       <c r="C3" t="n">
-        <v>5945</v>
+        <v>5578</v>
       </c>
       <c r="D3" t="n">
-        <v>7426</v>
+        <v>6405</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1881</v>
+        <v>1760</v>
       </c>
       <c r="C4" t="n">
-        <v>5857</v>
+        <v>3393</v>
       </c>
       <c r="D4" t="n">
-        <v>2408</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C5" t="n">
-        <v>2588</v>
+        <v>1253</v>
       </c>
       <c r="D5" t="n">
-        <v>1264</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4687</v>
+        <v>6533</v>
       </c>
       <c r="C2" t="n">
-        <v>6709</v>
+        <v>9499</v>
       </c>
       <c r="D2" t="n">
-        <v>37117</v>
+        <v>17831</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3307</v>
+        <v>3176</v>
       </c>
       <c r="C3" t="n">
-        <v>7608</v>
+        <v>5823</v>
       </c>
       <c r="D3" t="n">
-        <v>8575</v>
+        <v>7582</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2168</v>
+        <v>2078</v>
       </c>
       <c r="C4" t="n">
-        <v>5781</v>
+        <v>4464</v>
       </c>
       <c r="D4" t="n">
-        <v>3250</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>929</v>
+        <v>898</v>
       </c>
       <c r="C5" t="n">
-        <v>4197</v>
+        <v>2356</v>
       </c>
       <c r="D5" t="n">
-        <v>1423</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>1416</v>
+        <v>782</v>
       </c>
       <c r="D6" t="n">
-        <v>935</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5658</v>
+        <v>7956</v>
       </c>
       <c r="C2" t="n">
-        <v>5963</v>
+        <v>6245</v>
       </c>
       <c r="D2" t="n">
-        <v>34084</v>
+        <v>33242</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2866</v>
+        <v>3480</v>
       </c>
       <c r="C3" t="n">
-        <v>5880</v>
+        <v>6309</v>
       </c>
       <c r="D3" t="n">
-        <v>11361</v>
+        <v>8097</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1666</v>
+        <v>1619</v>
       </c>
       <c r="C4" t="n">
-        <v>5517</v>
+        <v>4236</v>
       </c>
       <c r="D4" t="n">
-        <v>3518</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>791</v>
+        <v>774</v>
       </c>
       <c r="C5" t="n">
-        <v>3601</v>
+        <v>2537</v>
       </c>
       <c r="D5" t="n">
-        <v>1373</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>1859</v>
+        <v>1061</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>770</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>541</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4648</v>
+        <v>6492</v>
       </c>
       <c r="C2" t="n">
-        <v>8045</v>
+        <v>3452</v>
       </c>
       <c r="D2" t="n">
-        <v>32185</v>
+        <v>26563</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3504</v>
+        <v>4766</v>
       </c>
       <c r="C3" t="n">
-        <v>5111</v>
+        <v>5388</v>
       </c>
       <c r="D3" t="n">
-        <v>14342</v>
+        <v>11725</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1969</v>
+        <v>2247</v>
       </c>
       <c r="C4" t="n">
-        <v>5614</v>
+        <v>5401</v>
       </c>
       <c r="D4" t="n">
-        <v>4992</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="C5" t="n">
-        <v>4611</v>
+        <v>3479</v>
       </c>
       <c r="D5" t="n">
-        <v>1743</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C6" t="n">
-        <v>2772</v>
+        <v>1873</v>
       </c>
       <c r="D6" t="n">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>1264</v>
+        <v>756</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>390</v>
+        <v>296</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3479</v>
+        <v>4967</v>
       </c>
       <c r="C2" t="n">
-        <v>6653</v>
+        <v>5435</v>
       </c>
       <c r="D2" t="n">
-        <v>29898</v>
+        <v>28669</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3329</v>
+        <v>4615</v>
       </c>
       <c r="C3" t="n">
-        <v>5763</v>
+        <v>3750</v>
       </c>
       <c r="D3" t="n">
-        <v>16044</v>
+        <v>13254</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2325</v>
+        <v>3004</v>
       </c>
       <c r="C4" t="n">
-        <v>5172</v>
+        <v>5281</v>
       </c>
       <c r="D4" t="n">
-        <v>6545</v>
+        <v>5377</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1311</v>
+        <v>1432</v>
       </c>
       <c r="C5" t="n">
-        <v>5044</v>
+        <v>4458</v>
       </c>
       <c r="D5" t="n">
-        <v>2234</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C6" t="n">
-        <v>3677</v>
+        <v>2681</v>
       </c>
       <c r="D6" t="n">
-        <v>997</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C7" t="n">
-        <v>2004</v>
+        <v>1346</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>818</v>
+        <v>530</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_76_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5877</v>
+        <v>4457</v>
       </c>
       <c r="C2" t="n">
-        <v>14908</v>
+        <v>7789</v>
       </c>
       <c r="D2" t="n">
-        <v>26209</v>
+        <v>25951</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3950</v>
+        <v>3075</v>
       </c>
       <c r="C3" t="n">
-        <v>4003</v>
+        <v>5708</v>
       </c>
       <c r="D3" t="n">
-        <v>14561</v>
+        <v>15606</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3202</v>
+        <v>2478</v>
       </c>
       <c r="C4" t="n">
-        <v>4326</v>
+        <v>6518</v>
       </c>
       <c r="D4" t="n">
-        <v>6523</v>
+        <v>7553</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1893</v>
+        <v>1697</v>
       </c>
       <c r="C5" t="n">
-        <v>4784</v>
+        <v>5718</v>
       </c>
       <c r="D5" t="n">
-        <v>2494</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>938</v>
+        <v>966</v>
       </c>
       <c r="C6" t="n">
-        <v>3522</v>
+        <v>3394</v>
       </c>
       <c r="D6" t="n">
-        <v>1109</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>461</v>
       </c>
       <c r="C7" t="n">
-        <v>1973</v>
+        <v>1532</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="C8" t="n">
-        <v>913</v>
+        <v>730</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
         <v>246</v>
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -954,7 +954,7 @@
         <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6393</v>
+        <v>5391</v>
       </c>
       <c r="C2" t="n">
-        <v>16493</v>
+        <v>14269</v>
       </c>
       <c r="D2" t="n">
-        <v>30023</v>
+        <v>21992</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3913</v>
+        <v>3007</v>
       </c>
       <c r="C3" t="n">
-        <v>7884</v>
+        <v>5847</v>
       </c>
       <c r="D3" t="n">
-        <v>15166</v>
+        <v>15964</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3016</v>
+        <v>2340</v>
       </c>
       <c r="C4" t="n">
-        <v>4080</v>
+        <v>5938</v>
       </c>
       <c r="D4" t="n">
-        <v>7636</v>
+        <v>8637</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2158</v>
+        <v>1800</v>
       </c>
       <c r="C5" t="n">
-        <v>4427</v>
+        <v>5967</v>
       </c>
       <c r="D5" t="n">
-        <v>3013</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1228</v>
+        <v>1173</v>
       </c>
       <c r="C6" t="n">
-        <v>4056</v>
+        <v>4354</v>
       </c>
       <c r="D6" t="n">
-        <v>1306</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>572</v>
+        <v>602</v>
       </c>
       <c r="C7" t="n">
-        <v>2635</v>
+        <v>2337</v>
       </c>
       <c r="D7" t="n">
-        <v>702</v>
+        <v>708</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C8" t="n">
-        <v>1369</v>
+        <v>1075</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>593</v>
+        <v>504</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="D10" t="n">
         <v>252</v>
@@ -1220,7 +1220,7 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
         <v>205</v>
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
         <v>164</v>
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1265,7 +1265,7 @@
         <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8588</v>
+        <v>6674</v>
       </c>
       <c r="C2" t="n">
-        <v>16171</v>
+        <v>9491</v>
       </c>
       <c r="D2" t="n">
-        <v>41573</v>
+        <v>34630</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4010</v>
+        <v>3252</v>
       </c>
       <c r="C3" t="n">
-        <v>10100</v>
+        <v>8224</v>
       </c>
       <c r="D3" t="n">
-        <v>15978</v>
+        <v>15665</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2911</v>
+        <v>2223</v>
       </c>
       <c r="C4" t="n">
-        <v>5599</v>
+        <v>5718</v>
       </c>
       <c r="D4" t="n">
-        <v>8414</v>
+        <v>9346</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2221</v>
+        <v>1798</v>
       </c>
       <c r="C5" t="n">
-        <v>4188</v>
+        <v>5830</v>
       </c>
       <c r="D5" t="n">
-        <v>3587</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1446</v>
+        <v>1297</v>
       </c>
       <c r="C6" t="n">
-        <v>4130</v>
+        <v>4923</v>
       </c>
       <c r="D6" t="n">
-        <v>1505</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C7" t="n">
-        <v>3179</v>
+        <v>3123</v>
       </c>
       <c r="D7" t="n">
-        <v>777</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C8" t="n">
-        <v>1864</v>
+        <v>1569</v>
       </c>
       <c r="D8" t="n">
         <v>479</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C9" t="n">
-        <v>875</v>
+        <v>711</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>390</v>
+        <v>351</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
         <v>167</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7767</v>
+        <v>6066</v>
       </c>
       <c r="C2" t="n">
-        <v>11125</v>
+        <v>6529</v>
       </c>
       <c r="D2" t="n">
-        <v>34025</v>
+        <v>28455</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5008</v>
+        <v>3944</v>
       </c>
       <c r="C3" t="n">
-        <v>13818</v>
+        <v>11318</v>
       </c>
       <c r="D3" t="n">
-        <v>17156</v>
+        <v>17157</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2052</v>
+        <v>1661</v>
       </c>
       <c r="C4" t="n">
-        <v>7084</v>
+        <v>8725</v>
       </c>
       <c r="D4" t="n">
-        <v>7971</v>
+        <v>8876</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1336</v>
+        <v>1198</v>
       </c>
       <c r="C5" t="n">
-        <v>4047</v>
+        <v>4824</v>
       </c>
       <c r="D5" t="n">
-        <v>2439</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C6" t="n">
-        <v>3115</v>
+        <v>3060</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>772</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>1826</v>
+        <v>1537</v>
       </c>
       <c r="D7" t="n">
         <v>469</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>857</v>
+        <v>696</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>382</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>163</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4553</v>
+        <v>3690</v>
       </c>
       <c r="C2" t="n">
-        <v>5183</v>
+        <v>3614</v>
       </c>
       <c r="D2" t="n">
-        <v>24851</v>
+        <v>20074</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5301</v>
+        <v>4158</v>
       </c>
       <c r="C3" t="n">
-        <v>11436</v>
+        <v>8313</v>
       </c>
       <c r="D3" t="n">
-        <v>18626</v>
+        <v>17869</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2779</v>
+        <v>2203</v>
       </c>
       <c r="C4" t="n">
-        <v>10311</v>
+        <v>10073</v>
       </c>
       <c r="D4" t="n">
-        <v>9127</v>
+        <v>9883</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1493</v>
+        <v>1316</v>
       </c>
       <c r="C5" t="n">
-        <v>5381</v>
+        <v>6481</v>
       </c>
       <c r="D5" t="n">
-        <v>3102</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="C6" t="n">
-        <v>3588</v>
+        <v>3856</v>
       </c>
       <c r="D6" t="n">
-        <v>935</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="C7" t="n">
-        <v>2327</v>
+        <v>2074</v>
       </c>
       <c r="D7" t="n">
         <v>517</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>1130</v>
+        <v>929</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>429</v>
+        <v>386</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4245</v>
+        <v>3447</v>
       </c>
       <c r="C2" t="n">
-        <v>13280</v>
+        <v>3010</v>
       </c>
       <c r="D2" t="n">
-        <v>22625</v>
+        <v>16555</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4239</v>
+        <v>3329</v>
       </c>
       <c r="C3" t="n">
-        <v>7603</v>
+        <v>5384</v>
       </c>
       <c r="D3" t="n">
-        <v>18220</v>
+        <v>16968</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3274</v>
+        <v>2616</v>
       </c>
       <c r="C4" t="n">
-        <v>10636</v>
+        <v>9098</v>
       </c>
       <c r="D4" t="n">
-        <v>10399</v>
+        <v>10885</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1796</v>
+        <v>1503</v>
       </c>
       <c r="C5" t="n">
-        <v>7540</v>
+        <v>8001</v>
       </c>
       <c r="D5" t="n">
-        <v>3933</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>999</v>
+        <v>935</v>
       </c>
       <c r="C6" t="n">
-        <v>4380</v>
+        <v>5015</v>
       </c>
       <c r="D6" t="n">
-        <v>1234</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C7" t="n">
-        <v>2880</v>
+        <v>2824</v>
       </c>
       <c r="D7" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C8" t="n">
-        <v>1609</v>
+        <v>1397</v>
       </c>
       <c r="D8" t="n">
         <v>353</v>
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>687</v>
+        <v>595</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="D10" t="n">
         <v>213</v>
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>35</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2556</v>
+        <v>2073</v>
       </c>
       <c r="C2" t="n">
-        <v>6422</v>
+        <v>1438</v>
       </c>
       <c r="D2" t="n">
-        <v>15792</v>
+        <v>11565</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4129</v>
+        <v>3239</v>
       </c>
       <c r="C3" t="n">
-        <v>9139</v>
+        <v>4398</v>
       </c>
       <c r="D3" t="n">
-        <v>18269</v>
+        <v>16544</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3571</v>
+        <v>2889</v>
       </c>
       <c r="C4" t="n">
-        <v>10577</v>
+        <v>8657</v>
       </c>
       <c r="D4" t="n">
-        <v>11295</v>
+        <v>11643</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1837</v>
+        <v>1589</v>
       </c>
       <c r="C5" t="n">
-        <v>9291</v>
+        <v>9425</v>
       </c>
       <c r="D5" t="n">
-        <v>4170</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>792</v>
+        <v>775</v>
       </c>
       <c r="C6" t="n">
-        <v>5241</v>
+        <v>5917</v>
       </c>
       <c r="D6" t="n">
-        <v>1215</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>2966</v>
+        <v>2798</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1146</v>
+        <v>1007</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
         <v>287</v>
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3269</v>
+        <v>3322</v>
       </c>
       <c r="C2" t="n">
-        <v>5898</v>
+        <v>3639</v>
       </c>
       <c r="D2" t="n">
-        <v>12099</v>
+        <v>10743</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2999</v>
+        <v>2346</v>
       </c>
       <c r="C3" t="n">
-        <v>7115</v>
+        <v>2728</v>
       </c>
       <c r="D3" t="n">
-        <v>16753</v>
+        <v>14913</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3344</v>
+        <v>2676</v>
       </c>
       <c r="C4" t="n">
-        <v>9708</v>
+        <v>6556</v>
       </c>
       <c r="D4" t="n">
-        <v>12022</v>
+        <v>12041</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2222</v>
+        <v>1874</v>
       </c>
       <c r="C5" t="n">
-        <v>9742</v>
+        <v>8980</v>
       </c>
       <c r="D5" t="n">
-        <v>5069</v>
+        <v>5409</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1050</v>
+        <v>985</v>
       </c>
       <c r="C6" t="n">
-        <v>6879</v>
+        <v>7369</v>
       </c>
       <c r="D6" t="n">
-        <v>1608</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C7" t="n">
-        <v>3892</v>
+        <v>4074</v>
       </c>
       <c r="D7" t="n">
-        <v>640</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1792</v>
+        <v>1658</v>
       </c>
       <c r="D8" t="n">
         <v>397</v>
@@ -3058,7 +3058,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>561</v>
+        <v>511</v>
       </c>
       <c r="D9" t="n">
         <v>294</v>
@@ -3072,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>175</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>32</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2334</v>
+        <v>2111</v>
       </c>
       <c r="C2" t="n">
-        <v>3243</v>
+        <v>2858</v>
       </c>
       <c r="D2" t="n">
-        <v>8978</v>
+        <v>7717</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2702</v>
+        <v>2329</v>
       </c>
       <c r="C3" t="n">
-        <v>6127</v>
+        <v>2799</v>
       </c>
       <c r="D3" t="n">
-        <v>15347</v>
+        <v>13744</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2966</v>
+        <v>2378</v>
       </c>
       <c r="C4" t="n">
-        <v>8789</v>
+        <v>5064</v>
       </c>
       <c r="D4" t="n">
-        <v>12362</v>
+        <v>12148</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2425</v>
+        <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>9808</v>
+        <v>8277</v>
       </c>
       <c r="D5" t="n">
-        <v>5746</v>
+        <v>5996</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1222</v>
+        <v>1139</v>
       </c>
       <c r="C6" t="n">
-        <v>7996</v>
+        <v>8160</v>
       </c>
       <c r="D6" t="n">
-        <v>1886</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C7" t="n">
-        <v>4830</v>
+        <v>5126</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>2270</v>
+        <v>2183</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>620</v>
+        <v>586</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>35</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4193</v>
+        <v>3898</v>
       </c>
       <c r="C2" t="n">
-        <v>4494</v>
+        <v>7129</v>
       </c>
       <c r="D2" t="n">
-        <v>15675</v>
+        <v>11312</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2172</v>
+        <v>1897</v>
       </c>
       <c r="C3" t="n">
-        <v>4501</v>
+        <v>2510</v>
       </c>
       <c r="D3" t="n">
-        <v>13676</v>
+        <v>12141</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2501</v>
+        <v>2051</v>
       </c>
       <c r="C4" t="n">
-        <v>7532</v>
+        <v>4001</v>
       </c>
       <c r="D4" t="n">
-        <v>12387</v>
+        <v>12008</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2399</v>
+        <v>1959</v>
       </c>
       <c r="C5" t="n">
-        <v>9212</v>
+        <v>6809</v>
       </c>
       <c r="D5" t="n">
-        <v>6341</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1485</v>
+        <v>1337</v>
       </c>
       <c r="C6" t="n">
-        <v>8593</v>
+        <v>8136</v>
       </c>
       <c r="D6" t="n">
-        <v>2343</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="7">
@@ -3652,10 +3652,10 @@
         <v>474</v>
       </c>
       <c r="C7" t="n">
-        <v>5945</v>
+        <v>6304</v>
       </c>
       <c r="D7" t="n">
-        <v>841</v>
+        <v>881</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>3144</v>
+        <v>3191</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1127</v>
+        <v>1107</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4727</v>
+        <v>4968</v>
       </c>
       <c r="C2" t="n">
-        <v>7028</v>
+        <v>6400</v>
       </c>
       <c r="D2" t="n">
-        <v>7980</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3063</v>
+        <v>2815</v>
       </c>
       <c r="C2" t="n">
-        <v>2660</v>
+        <v>4106</v>
       </c>
       <c r="D2" t="n">
-        <v>11662</v>
+        <v>8417</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3004</v>
+        <v>2592</v>
       </c>
       <c r="C3" t="n">
-        <v>4982</v>
+        <v>3765</v>
       </c>
       <c r="D3" t="n">
-        <v>14958</v>
+        <v>13095</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3473</v>
+        <v>2857</v>
       </c>
       <c r="C4" t="n">
-        <v>10599</v>
+        <v>6239</v>
       </c>
       <c r="D4" t="n">
-        <v>12462</v>
+        <v>12314</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1394</v>
+        <v>1271</v>
       </c>
       <c r="C5" t="n">
-        <v>12653</v>
+        <v>10837</v>
       </c>
       <c r="D5" t="n">
-        <v>5736</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="6">
@@ -4260,10 +4260,10 @@
         <v>437</v>
       </c>
       <c r="C6" t="n">
-        <v>7341</v>
+        <v>7692</v>
       </c>
       <c r="D6" t="n">
-        <v>1850</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>3081</v>
+        <v>3127</v>
       </c>
       <c r="D7" t="n">
-        <v>530</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1104</v>
+        <v>1084</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5926</v>
+        <v>6931</v>
       </c>
       <c r="C2" t="n">
-        <v>6399</v>
+        <v>4260</v>
       </c>
       <c r="D2" t="n">
-        <v>18428</v>
+        <v>16217</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2009</v>
+        <v>2112</v>
       </c>
       <c r="C3" t="n">
-        <v>3542</v>
+        <v>3276</v>
       </c>
       <c r="D3" t="n">
-        <v>1979</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4377</v>
+        <v>4359</v>
       </c>
       <c r="C2" t="n">
-        <v>8110</v>
+        <v>3096</v>
       </c>
       <c r="D2" t="n">
-        <v>17975</v>
+        <v>21234</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3256</v>
+        <v>3709</v>
       </c>
       <c r="C3" t="n">
-        <v>4448</v>
+        <v>3339</v>
       </c>
       <c r="D3" t="n">
-        <v>4596</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>906</v>
+        <v>951</v>
       </c>
       <c r="C4" t="n">
-        <v>2117</v>
+        <v>1962</v>
       </c>
       <c r="D4" t="n">
-        <v>1580</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="5">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4689</v>
+        <v>4790</v>
       </c>
       <c r="C2" t="n">
-        <v>7740</v>
+        <v>10897</v>
       </c>
       <c r="D2" t="n">
-        <v>17121</v>
+        <v>23777</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3130</v>
+        <v>3320</v>
       </c>
       <c r="C3" t="n">
-        <v>5578</v>
+        <v>2775</v>
       </c>
       <c r="D3" t="n">
-        <v>6405</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1760</v>
+        <v>1969</v>
       </c>
       <c r="C4" t="n">
-        <v>3393</v>
+        <v>2701</v>
       </c>
       <c r="D4" t="n">
-        <v>2111</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="C5" t="n">
-        <v>1253</v>
+        <v>1166</v>
       </c>
       <c r="D5" t="n">
-        <v>1210</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6533</v>
+        <v>5595</v>
       </c>
       <c r="C2" t="n">
-        <v>9499</v>
+        <v>14212</v>
       </c>
       <c r="D2" t="n">
-        <v>17831</v>
+        <v>31162</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3176</v>
+        <v>3300</v>
       </c>
       <c r="C3" t="n">
-        <v>5823</v>
+        <v>6141</v>
       </c>
       <c r="D3" t="n">
-        <v>7582</v>
+        <v>8633</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2078</v>
+        <v>2235</v>
       </c>
       <c r="C4" t="n">
-        <v>4464</v>
+        <v>2658</v>
       </c>
       <c r="D4" t="n">
-        <v>2830</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>898</v>
+        <v>1005</v>
       </c>
       <c r="C5" t="n">
-        <v>2356</v>
+        <v>1952</v>
       </c>
       <c r="D5" t="n">
-        <v>1317</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>782</v>
+        <v>738</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
         <v>659</v>
@@ -5546,7 +5546,7 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
         <v>216</v>
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7956</v>
+        <v>5513</v>
       </c>
       <c r="C2" t="n">
-        <v>6245</v>
+        <v>9081</v>
       </c>
       <c r="D2" t="n">
-        <v>33242</v>
+        <v>34075</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3480</v>
+        <v>3205</v>
       </c>
       <c r="C3" t="n">
-        <v>6309</v>
+        <v>8409</v>
       </c>
       <c r="D3" t="n">
-        <v>8097</v>
+        <v>10771</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1619</v>
+        <v>1706</v>
       </c>
       <c r="C4" t="n">
-        <v>4236</v>
+        <v>3730</v>
       </c>
       <c r="D4" t="n">
-        <v>3149</v>
+        <v>3198</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>774</v>
+        <v>844</v>
       </c>
       <c r="C5" t="n">
-        <v>2537</v>
+        <v>1697</v>
       </c>
       <c r="D5" t="n">
-        <v>1235</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="C6" t="n">
-        <v>1061</v>
+        <v>904</v>
       </c>
       <c r="D6" t="n">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D7" t="n">
         <v>513</v>
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5916,7 +5916,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6492</v>
+        <v>4589</v>
       </c>
       <c r="C2" t="n">
-        <v>3452</v>
+        <v>7228</v>
       </c>
       <c r="D2" t="n">
-        <v>26563</v>
+        <v>28840</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4766</v>
+        <v>3620</v>
       </c>
       <c r="C3" t="n">
-        <v>5388</v>
+        <v>7563</v>
       </c>
       <c r="D3" t="n">
-        <v>11725</v>
+        <v>13893</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2247</v>
+        <v>2159</v>
       </c>
       <c r="C4" t="n">
-        <v>5401</v>
+        <v>6482</v>
       </c>
       <c r="D4" t="n">
-        <v>4020</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1068</v>
+        <v>1131</v>
       </c>
       <c r="C5" t="n">
-        <v>3479</v>
+        <v>2835</v>
       </c>
       <c r="D5" t="n">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>482</v>
+        <v>534</v>
       </c>
       <c r="C6" t="n">
-        <v>1873</v>
+        <v>1349</v>
       </c>
       <c r="D6" t="n">
-        <v>848</v>
+        <v>835</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="C7" t="n">
-        <v>756</v>
+        <v>663</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D8" t="n">
         <v>388</v>
@@ -6168,7 +6168,7 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
         <v>281</v>
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4967</v>
+        <v>4155</v>
       </c>
       <c r="C2" t="n">
-        <v>5435</v>
+        <v>6684</v>
       </c>
       <c r="D2" t="n">
-        <v>28669</v>
+        <v>24825</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4615</v>
+        <v>3371</v>
       </c>
       <c r="C3" t="n">
-        <v>3750</v>
+        <v>6388</v>
       </c>
       <c r="D3" t="n">
-        <v>13254</v>
+        <v>15284</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3004</v>
+        <v>2486</v>
       </c>
       <c r="C4" t="n">
-        <v>5281</v>
+        <v>6959</v>
       </c>
       <c r="D4" t="n">
-        <v>5377</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="C5" t="n">
-        <v>4458</v>
+        <v>4771</v>
       </c>
       <c r="D5" t="n">
-        <v>1964</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>703</v>
+        <v>757</v>
       </c>
       <c r="C6" t="n">
-        <v>2681</v>
+        <v>2118</v>
       </c>
       <c r="D6" t="n">
-        <v>970</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="C7" t="n">
-        <v>1346</v>
+        <v>1012</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>530</v>
+        <v>480</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
         <v>295</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6507,7 +6507,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>

--- a/output/yearly_population_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_76_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4457</v>
+        <v>1353</v>
       </c>
       <c r="C2" t="n">
-        <v>7789</v>
+        <v>2852</v>
       </c>
       <c r="D2" t="n">
-        <v>25951</v>
+        <v>16659</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3075</v>
+        <v>2665</v>
       </c>
       <c r="C3" t="n">
-        <v>5708</v>
+        <v>6602</v>
       </c>
       <c r="D3" t="n">
-        <v>15606</v>
+        <v>12677</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2478</v>
+        <v>1975</v>
       </c>
       <c r="C4" t="n">
-        <v>6518</v>
+        <v>9239</v>
       </c>
       <c r="D4" t="n">
-        <v>7553</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1697</v>
+        <v>1017</v>
       </c>
       <c r="C5" t="n">
-        <v>5718</v>
+        <v>5576</v>
       </c>
       <c r="D5" t="n">
-        <v>2727</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>966</v>
+        <v>409</v>
       </c>
       <c r="C6" t="n">
-        <v>3394</v>
+        <v>1943</v>
       </c>
       <c r="D6" t="n">
-        <v>1118</v>
+        <v>752</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>461</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>1532</v>
+        <v>704</v>
       </c>
       <c r="D7" t="n">
-        <v>653</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>730</v>
+        <v>351</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5391</v>
+        <v>1888</v>
       </c>
       <c r="C2" t="n">
-        <v>14269</v>
+        <v>5217</v>
       </c>
       <c r="D2" t="n">
-        <v>21992</v>
+        <v>21131</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3007</v>
+        <v>1757</v>
       </c>
       <c r="C3" t="n">
-        <v>5847</v>
+        <v>4089</v>
       </c>
       <c r="D3" t="n">
-        <v>15964</v>
+        <v>12389</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2340</v>
+        <v>1980</v>
       </c>
       <c r="C4" t="n">
-        <v>5938</v>
+        <v>7629</v>
       </c>
       <c r="D4" t="n">
-        <v>8637</v>
+        <v>6892</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1800</v>
+        <v>1296</v>
       </c>
       <c r="C5" t="n">
-        <v>5967</v>
+        <v>7412</v>
       </c>
       <c r="D5" t="n">
-        <v>3359</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1173</v>
+        <v>608</v>
       </c>
       <c r="C6" t="n">
-        <v>4354</v>
+        <v>3720</v>
       </c>
       <c r="D6" t="n">
-        <v>1350</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>602</v>
+        <v>205</v>
       </c>
       <c r="C7" t="n">
-        <v>2337</v>
+        <v>1293</v>
       </c>
       <c r="D7" t="n">
-        <v>708</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>256</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>1075</v>
+        <v>509</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>504</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6674</v>
+        <v>1020</v>
       </c>
       <c r="C2" t="n">
-        <v>9491</v>
+        <v>2268</v>
       </c>
       <c r="D2" t="n">
-        <v>34630</v>
+        <v>14443</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3252</v>
+        <v>1725</v>
       </c>
       <c r="C3" t="n">
-        <v>8224</v>
+        <v>4356</v>
       </c>
       <c r="D3" t="n">
-        <v>15665</v>
+        <v>13120</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2223</v>
+        <v>2148</v>
       </c>
       <c r="C4" t="n">
-        <v>5718</v>
+        <v>6877</v>
       </c>
       <c r="D4" t="n">
-        <v>9346</v>
+        <v>7593</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1798</v>
+        <v>1298</v>
       </c>
       <c r="C5" t="n">
-        <v>5830</v>
+        <v>8417</v>
       </c>
       <c r="D5" t="n">
-        <v>4016</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1297</v>
+        <v>459</v>
       </c>
       <c r="C6" t="n">
-        <v>4923</v>
+        <v>4675</v>
       </c>
       <c r="D6" t="n">
-        <v>1589</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>741</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>3123</v>
+        <v>1236</v>
       </c>
       <c r="D7" t="n">
-        <v>788</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>344</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1569</v>
+        <v>480</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>711</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>212</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6066</v>
+        <v>1289</v>
       </c>
       <c r="C2" t="n">
-        <v>6529</v>
+        <v>6759</v>
       </c>
       <c r="D2" t="n">
-        <v>28455</v>
+        <v>12239</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3944</v>
+        <v>1204</v>
       </c>
       <c r="C3" t="n">
-        <v>11318</v>
+        <v>2921</v>
       </c>
       <c r="D3" t="n">
-        <v>17157</v>
+        <v>12407</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1661</v>
+        <v>1748</v>
       </c>
       <c r="C4" t="n">
-        <v>8725</v>
+        <v>5493</v>
       </c>
       <c r="D4" t="n">
-        <v>8876</v>
+        <v>8317</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1198</v>
+        <v>1493</v>
       </c>
       <c r="C5" t="n">
-        <v>4824</v>
+        <v>7568</v>
       </c>
       <c r="D5" t="n">
-        <v>2636</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>684</v>
+        <v>716</v>
       </c>
       <c r="C6" t="n">
-        <v>3060</v>
+        <v>6444</v>
       </c>
       <c r="D6" t="n">
-        <v>772</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>1537</v>
+        <v>2742</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>696</v>
+        <v>785</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>69</v>
+      </c>
+      <c r="D14" t="n">
         <v>67</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3690</v>
+        <v>802</v>
       </c>
       <c r="C2" t="n">
-        <v>3614</v>
+        <v>3462</v>
       </c>
       <c r="D2" t="n">
-        <v>20074</v>
+        <v>8698</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4158</v>
+        <v>1079</v>
       </c>
       <c r="C3" t="n">
-        <v>8313</v>
+        <v>4189</v>
       </c>
       <c r="D3" t="n">
-        <v>17869</v>
+        <v>11788</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2203</v>
+        <v>1450</v>
       </c>
       <c r="C4" t="n">
-        <v>10073</v>
+        <v>4376</v>
       </c>
       <c r="D4" t="n">
-        <v>9883</v>
+        <v>8732</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1316</v>
+        <v>1546</v>
       </c>
       <c r="C5" t="n">
-        <v>6481</v>
+        <v>6864</v>
       </c>
       <c r="D5" t="n">
-        <v>3385</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>811</v>
+        <v>864</v>
       </c>
       <c r="C6" t="n">
-        <v>3856</v>
+        <v>7099</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>297</v>
+        <v>195</v>
       </c>
       <c r="C7" t="n">
-        <v>2074</v>
+        <v>3981</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>929</v>
+        <v>1248</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>386</v>
+        <v>418</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3447</v>
+        <v>1491</v>
       </c>
       <c r="C2" t="n">
-        <v>3010</v>
+        <v>7911</v>
       </c>
       <c r="D2" t="n">
-        <v>16555</v>
+        <v>9427</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3329</v>
+        <v>814</v>
       </c>
       <c r="C3" t="n">
-        <v>5384</v>
+        <v>3435</v>
       </c>
       <c r="D3" t="n">
-        <v>16968</v>
+        <v>10575</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2616</v>
+        <v>1146</v>
       </c>
       <c r="C4" t="n">
-        <v>9098</v>
+        <v>4197</v>
       </c>
       <c r="D4" t="n">
-        <v>10885</v>
+        <v>8965</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1503</v>
+        <v>1385</v>
       </c>
       <c r="C5" t="n">
-        <v>8001</v>
+        <v>5598</v>
       </c>
       <c r="D5" t="n">
-        <v>4280</v>
+        <v>4702</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>935</v>
+        <v>1042</v>
       </c>
       <c r="C6" t="n">
-        <v>5015</v>
+        <v>7000</v>
       </c>
       <c r="D6" t="n">
-        <v>1299</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>437</v>
+        <v>385</v>
       </c>
       <c r="C7" t="n">
-        <v>2824</v>
+        <v>5262</v>
       </c>
       <c r="D7" t="n">
-        <v>573</v>
+        <v>772</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>1397</v>
+        <v>2331</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>595</v>
+        <v>722</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2073</v>
+        <v>1013</v>
       </c>
       <c r="C2" t="n">
-        <v>1438</v>
+        <v>4240</v>
       </c>
       <c r="D2" t="n">
-        <v>11565</v>
+        <v>6863</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3239</v>
+        <v>1204</v>
       </c>
       <c r="C3" t="n">
-        <v>4398</v>
+        <v>4891</v>
       </c>
       <c r="D3" t="n">
-        <v>16544</v>
+        <v>11261</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2889</v>
+        <v>1847</v>
       </c>
       <c r="C4" t="n">
-        <v>8657</v>
+        <v>6028</v>
       </c>
       <c r="D4" t="n">
-        <v>11643</v>
+        <v>9214</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1589</v>
+        <v>1039</v>
       </c>
       <c r="C5" t="n">
-        <v>9425</v>
+        <v>9082</v>
       </c>
       <c r="D5" t="n">
-        <v>4521</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>775</v>
+        <v>355</v>
       </c>
       <c r="C6" t="n">
-        <v>5917</v>
+        <v>6803</v>
       </c>
       <c r="D6" t="n">
-        <v>1273</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>2798</v>
+        <v>2284</v>
       </c>
       <c r="D7" t="n">
-        <v>573</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1007</v>
+        <v>707</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3322</v>
+        <v>536</v>
       </c>
       <c r="C2" t="n">
-        <v>3639</v>
+        <v>2399</v>
       </c>
       <c r="D2" t="n">
-        <v>10743</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2346</v>
+        <v>955</v>
       </c>
       <c r="C3" t="n">
-        <v>2728</v>
+        <v>4038</v>
       </c>
       <c r="D3" t="n">
-        <v>14913</v>
+        <v>9820</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2676</v>
+        <v>1289</v>
       </c>
       <c r="C4" t="n">
-        <v>6556</v>
+        <v>5122</v>
       </c>
       <c r="D4" t="n">
-        <v>12041</v>
+        <v>8905</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1874</v>
+        <v>977</v>
       </c>
       <c r="C5" t="n">
-        <v>8980</v>
+        <v>6790</v>
       </c>
       <c r="D5" t="n">
-        <v>5409</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>985</v>
+        <v>356</v>
       </c>
       <c r="C6" t="n">
-        <v>7369</v>
+        <v>6447</v>
       </c>
       <c r="D6" t="n">
-        <v>1692</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>4074</v>
+        <v>2995</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1658</v>
+        <v>835</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>511</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>126</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2111</v>
+        <v>486</v>
       </c>
       <c r="C2" t="n">
-        <v>2858</v>
+        <v>6577</v>
       </c>
       <c r="D2" t="n">
-        <v>7717</v>
+        <v>11725</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2329</v>
+        <v>637</v>
       </c>
       <c r="C3" t="n">
-        <v>2799</v>
+        <v>2741</v>
       </c>
       <c r="D3" t="n">
-        <v>13744</v>
+        <v>8562</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2378</v>
+        <v>986</v>
       </c>
       <c r="C4" t="n">
-        <v>5064</v>
+        <v>4461</v>
       </c>
       <c r="D4" t="n">
-        <v>12148</v>
+        <v>8715</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2025</v>
+        <v>1017</v>
       </c>
       <c r="C5" t="n">
-        <v>8277</v>
+        <v>5768</v>
       </c>
       <c r="D5" t="n">
-        <v>5996</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1139</v>
+        <v>579</v>
       </c>
       <c r="C6" t="n">
-        <v>8160</v>
+        <v>6613</v>
       </c>
       <c r="D6" t="n">
-        <v>2042</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>5126</v>
+        <v>4685</v>
       </c>
       <c r="D7" t="n">
-        <v>735</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>2183</v>
+        <v>1858</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>586</v>
+        <v>519</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3898</v>
+        <v>398</v>
       </c>
       <c r="C2" t="n">
-        <v>7129</v>
+        <v>11846</v>
       </c>
       <c r="D2" t="n">
-        <v>11312</v>
+        <v>13468</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1897</v>
+        <v>474</v>
       </c>
       <c r="C3" t="n">
-        <v>2510</v>
+        <v>4025</v>
       </c>
       <c r="D3" t="n">
-        <v>12141</v>
+        <v>8428</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2051</v>
+        <v>726</v>
       </c>
       <c r="C4" t="n">
-        <v>4001</v>
+        <v>3493</v>
       </c>
       <c r="D4" t="n">
-        <v>12008</v>
+        <v>8423</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1959</v>
+        <v>916</v>
       </c>
       <c r="C5" t="n">
-        <v>6809</v>
+        <v>5008</v>
       </c>
       <c r="D5" t="n">
-        <v>6640</v>
+        <v>5573</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1337</v>
+        <v>702</v>
       </c>
       <c r="C6" t="n">
-        <v>8136</v>
+        <v>6148</v>
       </c>
       <c r="D6" t="n">
-        <v>2509</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>474</v>
+        <v>307</v>
       </c>
       <c r="C7" t="n">
-        <v>6304</v>
+        <v>5571</v>
       </c>
       <c r="D7" t="n">
-        <v>881</v>
+        <v>956</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>3191</v>
+        <v>3103</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1107</v>
+        <v>1083</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4968</v>
+        <v>8154</v>
       </c>
       <c r="C2" t="n">
-        <v>6400</v>
+        <v>10277</v>
       </c>
       <c r="D2" t="n">
-        <v>6072</v>
+        <v>16228</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2815</v>
+        <v>1266</v>
       </c>
       <c r="C2" t="n">
-        <v>4106</v>
+        <v>18833</v>
       </c>
       <c r="D2" t="n">
-        <v>8417</v>
+        <v>13426</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2592</v>
+        <v>369</v>
       </c>
       <c r="C3" t="n">
-        <v>3765</v>
+        <v>6558</v>
       </c>
       <c r="D3" t="n">
-        <v>13095</v>
+        <v>8520</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2857</v>
+        <v>545</v>
       </c>
       <c r="C4" t="n">
-        <v>6239</v>
+        <v>3665</v>
       </c>
       <c r="D4" t="n">
-        <v>12314</v>
+        <v>8086</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1271</v>
+        <v>768</v>
       </c>
       <c r="C5" t="n">
-        <v>10837</v>
+        <v>4186</v>
       </c>
       <c r="D5" t="n">
-        <v>6010</v>
+        <v>5841</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>437</v>
+        <v>734</v>
       </c>
       <c r="C6" t="n">
-        <v>7692</v>
+        <v>5597</v>
       </c>
       <c r="D6" t="n">
-        <v>1980</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>414</v>
       </c>
       <c r="C7" t="n">
-        <v>3127</v>
+        <v>5811</v>
       </c>
       <c r="D7" t="n">
-        <v>542</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="C8" t="n">
-        <v>1084</v>
+        <v>4062</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>321</v>
+        <v>1874</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>603</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6931</v>
+        <v>6982</v>
       </c>
       <c r="C2" t="n">
-        <v>4260</v>
+        <v>8867</v>
       </c>
       <c r="D2" t="n">
-        <v>16217</v>
+        <v>21044</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2112</v>
+        <v>2626</v>
       </c>
       <c r="C3" t="n">
-        <v>3276</v>
+        <v>4058</v>
       </c>
       <c r="D3" t="n">
-        <v>1659</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4359</v>
+        <v>3754</v>
       </c>
       <c r="C2" t="n">
-        <v>3096</v>
+        <v>8084</v>
       </c>
       <c r="D2" t="n">
-        <v>21234</v>
+        <v>19883</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3709</v>
+        <v>4045</v>
       </c>
       <c r="C3" t="n">
-        <v>3339</v>
+        <v>5942</v>
       </c>
       <c r="D3" t="n">
-        <v>3982</v>
+        <v>5817</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>951</v>
+        <v>1237</v>
       </c>
       <c r="C4" t="n">
-        <v>1962</v>
+        <v>2542</v>
       </c>
       <c r="D4" t="n">
-        <v>1515</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4790</v>
+        <v>2995</v>
       </c>
       <c r="C2" t="n">
-        <v>10897</v>
+        <v>10460</v>
       </c>
       <c r="D2" t="n">
-        <v>23777</v>
+        <v>20531</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3320</v>
+        <v>3220</v>
       </c>
       <c r="C3" t="n">
-        <v>2775</v>
+        <v>6177</v>
       </c>
       <c r="D3" t="n">
-        <v>6455</v>
+        <v>7751</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1969</v>
+        <v>2284</v>
       </c>
       <c r="C4" t="n">
-        <v>2701</v>
+        <v>4512</v>
       </c>
       <c r="D4" t="n">
-        <v>1942</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>451</v>
+        <v>575</v>
       </c>
       <c r="C5" t="n">
-        <v>1166</v>
+        <v>1548</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5595</v>
+        <v>3935</v>
       </c>
       <c r="C2" t="n">
-        <v>14212</v>
+        <v>7347</v>
       </c>
       <c r="D2" t="n">
-        <v>31162</v>
+        <v>15554</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3300</v>
+        <v>2573</v>
       </c>
       <c r="C3" t="n">
-        <v>6141</v>
+        <v>7427</v>
       </c>
       <c r="D3" t="n">
-        <v>8633</v>
+        <v>9237</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2235</v>
+        <v>2375</v>
       </c>
       <c r="C4" t="n">
-        <v>2658</v>
+        <v>5301</v>
       </c>
       <c r="D4" t="n">
-        <v>2687</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1005</v>
+        <v>1206</v>
       </c>
       <c r="C5" t="n">
-        <v>1952</v>
+        <v>3137</v>
       </c>
       <c r="D5" t="n">
-        <v>1297</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="C6" t="n">
-        <v>738</v>
+        <v>938</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5513</v>
+        <v>3021</v>
       </c>
       <c r="C2" t="n">
-        <v>9081</v>
+        <v>8535</v>
       </c>
       <c r="D2" t="n">
-        <v>34075</v>
+        <v>19505</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3205</v>
+        <v>2631</v>
       </c>
       <c r="C3" t="n">
-        <v>8409</v>
+        <v>6441</v>
       </c>
       <c r="D3" t="n">
-        <v>10771</v>
+        <v>9546</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1706</v>
+        <v>2141</v>
       </c>
       <c r="C4" t="n">
-        <v>3730</v>
+        <v>6313</v>
       </c>
       <c r="D4" t="n">
-        <v>3198</v>
+        <v>4369</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>844</v>
+        <v>1525</v>
       </c>
       <c r="C5" t="n">
-        <v>1697</v>
+        <v>4142</v>
       </c>
       <c r="D5" t="n">
-        <v>1225</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>301</v>
+        <v>641</v>
       </c>
       <c r="C6" t="n">
-        <v>904</v>
+        <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>902</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>348</v>
+        <v>609</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4589</v>
+        <v>2752</v>
       </c>
       <c r="C2" t="n">
-        <v>7228</v>
+        <v>7517</v>
       </c>
       <c r="D2" t="n">
-        <v>28840</v>
+        <v>30267</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3620</v>
+        <v>2316</v>
       </c>
       <c r="C3" t="n">
-        <v>7563</v>
+        <v>6512</v>
       </c>
       <c r="D3" t="n">
-        <v>13893</v>
+        <v>10258</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2159</v>
+        <v>2040</v>
       </c>
       <c r="C4" t="n">
-        <v>6482</v>
+        <v>6183</v>
       </c>
       <c r="D4" t="n">
-        <v>4596</v>
+        <v>5039</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1131</v>
+        <v>1593</v>
       </c>
       <c r="C5" t="n">
-        <v>2835</v>
+        <v>5097</v>
       </c>
       <c r="D5" t="n">
-        <v>1585</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>534</v>
+        <v>930</v>
       </c>
       <c r="C6" t="n">
-        <v>1349</v>
+        <v>2980</v>
       </c>
       <c r="D6" t="n">
-        <v>835</v>
+        <v>995</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>177</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>663</v>
+        <v>1241</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>291</v>
+        <v>436</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4155</v>
+        <v>2596</v>
       </c>
       <c r="C2" t="n">
-        <v>6684</v>
+        <v>4750</v>
       </c>
       <c r="D2" t="n">
-        <v>24825</v>
+        <v>23926</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3371</v>
+        <v>3316</v>
       </c>
       <c r="C3" t="n">
-        <v>6388</v>
+        <v>9710</v>
       </c>
       <c r="D3" t="n">
-        <v>15284</v>
+        <v>11586</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2486</v>
+        <v>1471</v>
       </c>
       <c r="C4" t="n">
-        <v>6959</v>
+        <v>8632</v>
       </c>
       <c r="D4" t="n">
-        <v>6241</v>
+        <v>4757</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1428</v>
+        <v>859</v>
       </c>
       <c r="C5" t="n">
-        <v>4771</v>
+        <v>2920</v>
       </c>
       <c r="D5" t="n">
-        <v>2070</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>757</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>2118</v>
+        <v>1216</v>
       </c>
       <c r="D6" t="n">
-        <v>960</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>310</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>1012</v>
+        <v>427</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>480</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
